--- a/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,74</t>
+          <t>-2,77; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,89</t>
+          <t>-3,78; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,72</t>
+          <t>-2,09; 4,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,66</t>
+          <t>-0,01; 5,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,88</t>
+          <t>-2,11; 0,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,29</t>
+          <t>-0,96; 5,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,24</t>
+          <t>-0,58; 3,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,44</t>
+          <t>-2,22; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,78</t>
+          <t>-1,05; 3,27</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 795,4</t>
+          <t>-100,0; 826,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,91; —</t>
+          <t>-53,11; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 500,69</t>
+          <t>-42,11; 504,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,78</t>
+          <t>-100,0; 118,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 525,02</t>
+          <t>-67,78; 573,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,06</t>
+          <t>-2,01; 2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,5</t>
+          <t>-2,4; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,51</t>
+          <t>-2,79; 0,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,03</t>
+          <t>-0,28; 4,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,97</t>
+          <t>-0,64; 3,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,7</t>
+          <t>-1,56; 1,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,33</t>
+          <t>-0,77; 2,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,71</t>
+          <t>-0,95; 1,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,7</t>
+          <t>-1,66; 0,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 276,75</t>
+          <t>-77,01; 450,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,26; 230,81</t>
+          <t>-82,66; 243,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-93,59; 110,87</t>
+          <t>-100,0; 154,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>-48,27; 1550,09</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-50,21; 1002,66</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-60,63; 925,4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 311,86</t>
+          <t>-40,66; 321,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 221,92</t>
+          <t>-52,35; 240,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 112,76</t>
+          <t>-80,83; 147,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,03</t>
+          <t>-1,4; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,14</t>
+          <t>-2,43; 1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,26</t>
+          <t>-1,88; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,88</t>
+          <t>-0,26; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,66</t>
+          <t>-1,45; 2,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,55</t>
+          <t>-0,53; 4,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,15</t>
+          <t>-0,15; 3,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,4</t>
+          <t>-1,31; 1,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,88</t>
+          <t>-0,7; 2,71</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 941,53</t>
+          <t>-82,83; 1162,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,39; —</t>
+          <t>-87,06; 808,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,16; —</t>
+          <t>-66,26; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 721,5</t>
+          <t>-20,84; 749,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 354,55</t>
+          <t>-79,4; 298,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 640,14</t>
+          <t>-49,54; 490,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,71</t>
+          <t>-1,35; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,18</t>
+          <t>-1,26; 2,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,06</t>
+          <t>-1,64; 1,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>-3,07; 1,01</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>-3,13; 1,06</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>-3,04; 0,86</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,98; 1,08</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 0,82</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,91</t>
+          <t>-1,56; 0,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,08</t>
+          <t>-1,55; 0,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,61</t>
+          <t>-1,85; 0,59</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 210,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 285,21</t>
+          <t>-100,0; 308,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 389,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 182,43</t>
+          <t>-79,05; 176,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,92; 217,74</t>
+          <t>-76,3; 197,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,95; 148,53</t>
+          <t>-86,77; 130,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,26</t>
+          <t>-1,0; 1,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-1,23; 0,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,05</t>
+          <t>-1,12; 0,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,33</t>
+          <t>0,22; 2,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,17</t>
+          <t>-0,73; 1,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,4</t>
+          <t>-0,78; 1,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,48</t>
+          <t>-0,03; 1,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,69</t>
+          <t>-0,73; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,83</t>
+          <t>-0,69; 0,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 143,43</t>
+          <t>-50,81; 117,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 89,53</t>
+          <t>-65,32; 77,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 121,12</t>
+          <t>-58,81; 93,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 333,44</t>
+          <t>4,84; 352,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 153,93</t>
+          <t>-46,48; 146,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 175,68</t>
+          <t>-51,33; 179,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 165,65</t>
+          <t>-5,32; 157,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 71,46</t>
+          <t>-44,43; 64,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 86,84</t>
+          <t>-42,23; 79,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,42</t>
+          <t>-2,81; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,92</t>
+          <t>-3,53; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,12</t>
+          <t>-2,12; 4,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,33</t>
+          <t>0,19; 5,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,88</t>
+          <t>-2,23; 0,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,47</t>
+          <t>-0,96; 4,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,31</t>
+          <t>-0,62; 3,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,45</t>
+          <t>-2,28; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,27</t>
+          <t>-1,24; 2,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 564,43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 804,52</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-49,12; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 826,06</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-53,11; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 504,79</t>
+          <t>-42,06; 465,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 118,25</t>
+          <t>-100,0; 135,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 573,67</t>
+          <t>-76,87; 444,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,05</t>
+          <t>-2,07; 2,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,43</t>
+          <t>-2,45; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,6</t>
+          <t>-2,75; 0,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,01</t>
+          <t>-0,29; 4,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,21</t>
+          <t>-0,51; 3,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,64</t>
+          <t>-1,27; 1,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,31</t>
+          <t>-0,64; 2,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,82</t>
+          <t>-0,96; 1,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,7</t>
+          <t>-1,68; 0,66</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,01; 450,82</t>
+          <t>-79,4; 315,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 243,89</t>
+          <t>-86,53; 179,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 1550,09</t>
+          <t>-38,13; 1341,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 1002,66</t>
+          <t>-65,18; 948,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 321,08</t>
+          <t>-37,09; 284,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,35; 240,01</t>
+          <t>-48,87; 238,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 147,12</t>
+          <t>-82,59; 115,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,86</t>
+          <t>-1,43; 2,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,1</t>
+          <t>-2,45; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,79</t>
+          <t>-1,39; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,67</t>
+          <t>-0,36; 4,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,47</t>
+          <t>-1,4; 2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,78</t>
+          <t>-0,84; 4,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,26</t>
+          <t>-0,16; 3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,26</t>
+          <t>-1,36; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,71</t>
+          <t>-0,52; 2,84</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,83; 1162,41</t>
+          <t>-82,46; 1031,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 808,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,26; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 749,81</t>
+          <t>-29,12; 682,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,4; 298,93</t>
+          <t>-79,7; 296,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 490,31</t>
+          <t>-51,61; 565,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,65</t>
+          <t>-1,34; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,01</t>
+          <t>-1,2; 2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,07</t>
+          <t>-1,72; 1,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,01</t>
+          <t>-3,04; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,06</t>
+          <t>-2,93; 0,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,86</t>
+          <t>-2,97; 0,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,93</t>
+          <t>-1,64; 0,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,99</t>
+          <t>-1,49; 1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,59</t>
+          <t>-1,82; 0,68</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 210,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 308,23</t>
+          <t>-100,0; 176,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 389,57</t>
+          <t>-100,0; 283,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 176,85</t>
+          <t>-81,21; 151,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,3; 197,4</t>
+          <t>-75,97; 187,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-86,77; 130,93</t>
+          <t>-89,45; 182,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,14</t>
+          <t>-0,81; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,64</t>
+          <t>-1,22; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,92</t>
+          <t>-1,1; 1,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,51</t>
+          <t>0,08; 2,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,07</t>
+          <t>-0,79; 1,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,37</t>
+          <t>-0,77; 1,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,51</t>
+          <t>-0,09; 1,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,62</t>
+          <t>-0,75; 0,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,76</t>
+          <t>-0,7; 0,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 117,38</t>
+          <t>-44,54; 139,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 77,94</t>
+          <t>-64,16; 73,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 93,71</t>
+          <t>-56,9; 118,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,84; 352,55</t>
+          <t>-3,91; 321,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 146,55</t>
+          <t>-49,93; 136,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 179,78</t>
+          <t>-51,55; 205,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 157,97</t>
+          <t>-7,22; 143,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 64,01</t>
+          <t>-44,36; 59,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 79,44</t>
+          <t>-44,86; 85,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,52</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,79</t>
+          <t>0,04; 5,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,92</t>
+          <t>-2,21; 0,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,3</t>
+          <t>-1,17; 3,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,44</t>
+          <t>-2,56; 2,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,89</t>
+          <t>-3,6; 0,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,85</t>
+          <t>-2,34; 3,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,19</t>
+          <t>-0,71; 3,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,45</t>
+          <t>-2,2; 0,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,94</t>
+          <t>-1,32; 2,57</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>282,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-49,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-11,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-52,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>282,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-49,26%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 564,43</t>
+          <t>-59,91; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 804,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,12; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 749,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 465,57</t>
+          <t>-39,07; 500,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 135,47</t>
+          <t>-100,0; 114,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,87; 444,43</t>
+          <t>-73,0; 474,16</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,43</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,01</t>
+          <t>-0,22; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,32</t>
+          <t>-0,5; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,73</t>
+          <t>-1,25; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,01</t>
+          <t>-2,06; 2,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,35</t>
+          <t>-2,2; 1,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,69</t>
+          <t>-2,72; 0,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,14</t>
+          <t>-0,63; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,69</t>
+          <t>-0,92; 1,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,66</t>
+          <t>-1,58; 0,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>176,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>118,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-9,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-23,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-55,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>176,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>118,82%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>-53,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-26,86%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,4; 315,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,53; 179,97</t>
+          <t>-60,63; 925,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 1341,13</t>
+          <t>-77,04; 276,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,18; 948,46</t>
+          <t>-81,26; 230,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,86; 137,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 284,91</t>
+          <t>-38,32; 311,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 238,74</t>
+          <t>-48,8; 221,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 115,05</t>
+          <t>-82,29; 135,01</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,89</t>
+          <t>-0,1; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,07</t>
+          <t>-1,41; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,89</t>
+          <t>-0,73; 5,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,82</t>
+          <t>-1,56; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,59</t>
+          <t>-2,52; 1,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,53</t>
+          <t>-1,23; 3,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,11</t>
+          <t>-0,19; 3,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,33</t>
+          <t>-1,31; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,84</t>
+          <t>-0,5; 3,49</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>215,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69,02%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165,74%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>54,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-38,57%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>215,45%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>153,08%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>115,32%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 1031,84</t>
+          <t>-58,16; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-77,6; 941,53</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,06; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 682,63</t>
+          <t>-23,6; 721,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,7; 296,09</t>
+          <t>-75,8; 354,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 565,89</t>
+          <t>-49,36; 730,14</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,86</t>
+          <t>-3,04; 0,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,22</t>
+          <t>-2,98; 1,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,24</t>
+          <t>-2,9; 0,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,05</t>
+          <t>-1,27; 1,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,86</t>
+          <t>-1,2; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,75</t>
+          <t>-1,86; 0,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,91</t>
+          <t>-1,68; 0,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,06</t>
+          <t>-1,56; 1,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,68</t>
+          <t>-1,85; 0,55</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-43,54%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,77%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-56,54%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>26,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>46,73%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-11,26%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-43,54%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-42,77%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-56,28%</t>
+          <t>-22,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-42,52%</t>
+          <t>-46,15%</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 285,21</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 176,03</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 151,01</t>
+          <t>-81,59; 182,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 187,0</t>
+          <t>-75,92; 217,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,45; 182,6</t>
+          <t>-90,46; 126,88</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,22</t>
+          <t>0,04; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,68</t>
+          <t>-0,75; 1,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,0</t>
+          <t>-0,81; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,42</t>
+          <t>-0,87; 1,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,03</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,46</t>
+          <t>-1,06; 1,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,44</t>
+          <t>-0,06; 1,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,57</t>
+          <t>-0,75; 0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,84</t>
+          <t>-0,66; 0,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>102,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-22,18%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>-2,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 139,71</t>
+          <t>-3,22; 333,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 73,01</t>
+          <t>-46,01; 153,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 118,48</t>
+          <t>-51,11; 176,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 321,08</t>
+          <t>-47,55; 143,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 136,18</t>
+          <t>-64,08; 89,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 205,32</t>
+          <t>-58,94; 130,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 143,26</t>
+          <t>-5,73; 165,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 59,28</t>
+          <t>-43,99; 71,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 85,7</t>
+          <t>-40,78; 91,79</t>
         </is>
       </c>
     </row>
